--- a/StructureDefinition-openimis-activity-definition.xlsx
+++ b/StructureDefinition-openimis-activity-definition.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-08-26T15:39:34+00:00</t>
+    <t>2025-09-08T11:14:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -11487,7 +11487,7 @@
         <v>79</v>
       </c>
       <c r="G74" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H74" t="s" s="2">
         <v>22</v>
@@ -11943,7 +11943,7 @@
         <v>79</v>
       </c>
       <c r="G78" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H78" t="s" s="2">
         <v>22</v>
@@ -12169,7 +12169,7 @@
         <v>79</v>
       </c>
       <c r="G80" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H80" t="s" s="2">
         <v>22</v>
@@ -12287,7 +12287,7 @@
         <v>79</v>
       </c>
       <c r="G81" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H81" t="s" s="2">
         <v>22</v>
@@ -12517,7 +12517,7 @@
         <v>79</v>
       </c>
       <c r="G83" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H83" t="s" s="2">
         <v>22</v>
@@ -12633,7 +12633,7 @@
         <v>79</v>
       </c>
       <c r="G84" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H84" t="s" s="2">
         <v>22</v>
@@ -12747,7 +12747,7 @@
         <v>79</v>
       </c>
       <c r="G85" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H85" t="s" s="2">
         <v>22</v>
@@ -17511,7 +17511,7 @@
         <v>79</v>
       </c>
       <c r="G127" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H127" t="s" s="2">
         <v>22</v>
@@ -17625,7 +17625,7 @@
         <v>79</v>
       </c>
       <c r="G128" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H128" t="s" s="2">
         <v>22</v>
@@ -17739,7 +17739,7 @@
         <v>79</v>
       </c>
       <c r="G129" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H129" t="s" s="2">
         <v>22</v>
@@ -17851,7 +17851,7 @@
         <v>79</v>
       </c>
       <c r="G130" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H130" t="s" s="2">
         <v>22</v>
@@ -18083,7 +18083,7 @@
         <v>79</v>
       </c>
       <c r="G132" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H132" t="s" s="2">
         <v>22</v>
@@ -18197,7 +18197,7 @@
         <v>79</v>
       </c>
       <c r="G133" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H133" t="s" s="2">
         <v>22</v>
@@ -18313,7 +18313,7 @@
         <v>79</v>
       </c>
       <c r="G134" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H134" t="s" s="2">
         <v>22</v>
@@ -18543,7 +18543,7 @@
         <v>79</v>
       </c>
       <c r="G136" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H136" t="s" s="2">
         <v>22</v>
@@ -18655,7 +18655,7 @@
         <v>79</v>
       </c>
       <c r="G137" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H137" t="s" s="2">
         <v>22</v>
@@ -18767,7 +18767,7 @@
         <v>79</v>
       </c>
       <c r="G138" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H138" t="s" s="2">
         <v>22</v>
@@ -18881,7 +18881,7 @@
         <v>79</v>
       </c>
       <c r="G139" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H139" t="s" s="2">
         <v>22</v>
@@ -18995,7 +18995,7 @@
         <v>79</v>
       </c>
       <c r="G140" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H140" t="s" s="2">
         <v>22</v>
@@ -19111,7 +19111,7 @@
         <v>79</v>
       </c>
       <c r="G141" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H141" t="s" s="2">
         <v>22</v>
@@ -19337,7 +19337,7 @@
         <v>79</v>
       </c>
       <c r="G143" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H143" t="s" s="2">
         <v>22</v>
@@ -19451,7 +19451,7 @@
         <v>79</v>
       </c>
       <c r="G144" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H144" t="s" s="2">
         <v>22</v>
@@ -19567,7 +19567,7 @@
         <v>79</v>
       </c>
       <c r="G145" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H145" t="s" s="2">
         <v>22</v>
@@ -19679,7 +19679,7 @@
         <v>79</v>
       </c>
       <c r="G146" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H146" t="s" s="2">
         <v>22</v>
@@ -19791,7 +19791,7 @@
         <v>79</v>
       </c>
       <c r="G147" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H147" t="s" s="2">
         <v>22</v>
@@ -22743,7 +22743,7 @@
         <v>79</v>
       </c>
       <c r="G173" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H173" t="s" s="2">
         <v>22</v>
@@ -22859,7 +22859,7 @@
         <v>79</v>
       </c>
       <c r="G174" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H174" t="s" s="2">
         <v>22</v>
@@ -23873,7 +23873,7 @@
         <v>79</v>
       </c>
       <c r="G183" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H183" t="s" s="2">
         <v>22</v>
@@ -23985,7 +23985,7 @@
         <v>79</v>
       </c>
       <c r="G184" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H184" t="s" s="2">
         <v>22</v>
@@ -24097,7 +24097,7 @@
         <v>79</v>
       </c>
       <c r="G185" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H185" t="s" s="2">
         <v>22</v>
@@ -24211,7 +24211,7 @@
         <v>79</v>
       </c>
       <c r="G186" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H186" t="s" s="2">
         <v>22</v>
@@ -24327,7 +24327,7 @@
         <v>79</v>
       </c>
       <c r="G187" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H187" t="s" s="2">
         <v>22</v>
@@ -24441,7 +24441,7 @@
         <v>79</v>
       </c>
       <c r="G188" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H188" t="s" s="2">
         <v>22</v>
@@ -24555,7 +24555,7 @@
         <v>79</v>
       </c>
       <c r="G189" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H189" t="s" s="2">
         <v>22</v>
@@ -24667,7 +24667,7 @@
         <v>79</v>
       </c>
       <c r="G190" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H190" t="s" s="2">
         <v>22</v>
@@ -24781,7 +24781,7 @@
         <v>79</v>
       </c>
       <c r="G191" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H191" t="s" s="2">
         <v>22</v>

--- a/StructureDefinition-openimis-activity-definition.xlsx
+++ b/StructureDefinition-openimis-activity-definition.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-09-08T11:14:40+00:00</t>
+    <t>2025-09-08T11:37:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-openimis-activity-definition.xlsx
+++ b/StructureDefinition-openimis-activity-definition.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-09-08T11:37:47+00:00</t>
+    <t>2025-09-08T11:49:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
